--- a/data/models/caterpillar.xlsx
+++ b/data/models/caterpillar.xlsx
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>710.9</v>
+        <v>703.84</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>12</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">B11*B12</f>
-        <v>328.79125</v>
+        <v>325.526</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">B13/(B13+B14)*B10+B14/(B13+B14)*B15*(1-B16)</f>
-        <v>0.0968319105848076</v>
+        <v>0.0968132997153266</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1080,15 +1080,15 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">Bear!$B$43</f>
-        <v>255.661627251414</v>
+        <v>255.720950553368</v>
       </c>
       <c r="C21" s="21" t="n">
         <f aca="false">Base!$B$43</f>
-        <v>441.856294200269</v>
+        <v>441.979336256059</v>
       </c>
       <c r="D21" s="21" t="n">
         <f aca="false">Bull!$B$43</f>
-        <v>675.717210963022</v>
+        <v>675.944564148863</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,B22:D22)</f>
-        <v>453.772856653744</v>
+        <v>453.906046803587</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1119,7 +1119,7 @@
         <v>29</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>710.9</v>
+        <v>703.84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">C23/C24-1</f>
-        <v>-0.361692422768683</v>
+        <v>-0.355100524545938</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0968319105848076</v>
+        <v>0.0968132997153266</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1881,43 +1881,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.954838587079538</v>
+        <v>0.9548466879573</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.870542311784527</v>
+        <v>0.870564469089796</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.793687987542569</v>
+        <v>0.793721656471295</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.723618614559994</v>
+        <v>0.723661590060316</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.659735195135028</v>
+        <v>0.659785571754226</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.601491613043307</v>
+        <v>0.601547749216271</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.548389964987984</v>
+        <v>0.54845045129595</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.499976304204711</v>
+        <v>0.500039935181583</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.455836759835091</v>
+        <v>0.455902508942375</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.415593998894551</v>
+        <v>0.415660996325175</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1926,43 +1926,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>10.7187391656875</v>
+        <v>10.7188301037758</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>10.9630654026309</v>
+        <v>10.9633444378753</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>10.7869899760836</v>
+        <v>10.7874475694986</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>10.5718426748241</v>
+        <v>10.5724705335042</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>10.1861844175389</v>
+        <v>10.1869622228421</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>9.77946262013814</v>
+        <v>9.78037532048713</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>9.35525364564652</v>
+        <v>9.35628551126996</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>8.91718399316115</v>
+        <v>8.9183188652014</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>8.46887842284656</v>
+        <v>8.47009995924964</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>8.0139100123696</v>
+        <v>8.01520192558659</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>97.7615103309269</v>
+        <v>97.7693364492908</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>268.524151054965</v>
+        <v>268.598948557095</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>111.597025736697</v>
+        <v>111.646106569136</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>209.358536067624</v>
+        <v>209.415443018427</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>204.358536067624</v>
+        <v>204.415443018427</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>441.856294200269</v>
+        <v>441.979336256059</v>
       </c>
     </row>
   </sheetData>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.106831910584808</v>
+        <v>0.106813299715327</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,43 +2698,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.950515414478615</v>
+        <v>0.950523405819142</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.858771241946213</v>
+        <v>0.858792902166624</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.775882257941471</v>
+        <v>0.77591487415945</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.70099375571086</v>
+        <v>0.701035011378176</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.633333525178617</v>
+        <v>0.633381448848223</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.572203890330545</v>
+        <v>0.572256810621203</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.516974515153086</v>
+        <v>0.517031021192453</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.46707590394637</v>
+        <v>0.467134810654546</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.421993528989948</v>
+        <v>0.422053846637634</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.381262525008863</v>
+        <v>0.381323432548368</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2743,43 +2743,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>9.83099082886942</v>
+        <v>9.83107348170623</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>8.61318013941329</v>
+        <v>8.61339738397289</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>7.92197990332582</v>
+        <v>7.92231292424582</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>7.29514922463126</v>
+        <v>7.29557856689997</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>6.72611369281191</v>
+        <v>6.72662265063197</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>6.20902134577581</v>
+        <v>6.20959558726538</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>5.73865838562101</v>
+        <v>5.73928562902884</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>5.31037524453429</v>
+        <v>5.31104497877276</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>4.92002167161115</v>
+        <v>4.92072491493933</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>4.56388968903394</v>
+        <v>4.56461878060024</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>67.1293801256279</v>
+        <v>67.1342548980634</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>147.179748329177</v>
+        <v>147.215408079462</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>56.1141224781512</v>
+        <v>56.1366847328693</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>123.243502603779</v>
+        <v>123.270939630933</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>118.243502603779</v>
+        <v>118.270939630933</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>255.661627251414</v>
+        <v>255.720950553368</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="B18" s="29" t="n">
         <f aca="false">Summary!$B$17+B17</f>
-        <v>0.0868319105848076</v>
+        <v>0.0868132997153266</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3515,43 +3515,43 @@
       </c>
       <c r="B33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(B24-0.5)</f>
-        <v>0.959221289887701</v>
+        <v>0.959229502828144</v>
       </c>
       <c r="C33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(C24-0.5)</f>
-        <v>0.882584768210899</v>
+        <v>0.882607438719602</v>
       </c>
       <c r="D33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(D24-0.5)</f>
-        <v>0.812071084420031</v>
+        <v>0.812105850149963</v>
       </c>
       <c r="E33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(E24-0.5)</f>
-        <v>0.747191057339371</v>
+        <v>0.747235841117036</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(F24-0.5)</f>
-        <v>0.687494588686965</v>
+        <v>0.687547568025495</v>
       </c>
       <c r="G33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(G24-0.5)</f>
-        <v>0.632567540565712</v>
+        <v>0.63262712022901</v>
       </c>
       <c r="H33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(H24-0.5)</f>
-        <v>0.582028862425779</v>
+        <v>0.582093649750805</v>
       </c>
       <c r="I33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(I24-0.5)</f>
-        <v>0.535527947566978</v>
+        <v>0.535596730278581</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(J24-0.5)</f>
-        <v>0.492742200842096</v>
+        <v>0.492813927119656</v>
       </c>
       <c r="K33" s="32" t="n">
         <f aca="false">1/(1+$B$18)^(K24-0.5)</f>
-        <v>0.453374800687402</v>
+        <v>0.453448561265068</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3560,43 +3560,43 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">B32*B33</f>
-        <v>11.3051902783585</v>
+        <v>11.3052870744319</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">C32*C33</f>
-        <v>12.1491860294842</v>
+        <v>12.1494980994831</v>
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">D32*D33</f>
-        <v>12.6545755938618</v>
+        <v>12.6551173513088</v>
       </c>
       <c r="E34" s="14" t="n">
         <f aca="false">E32*E33</f>
-        <v>13.0616527943754</v>
+        <v>13.0624356599477</v>
       </c>
       <c r="F34" s="14" t="n">
         <f aca="false">F32*F33</f>
-        <v>13.1147071418695</v>
+        <v>13.1157177803833</v>
       </c>
       <c r="G34" s="14" t="n">
         <f aca="false">G32*G33</f>
-        <v>13.0606992777111</v>
+        <v>13.0619294262968</v>
       </c>
       <c r="H34" s="14" t="n">
         <f aca="false">H32*H33</f>
-        <v>12.90010469605</v>
+        <v>12.901540644213</v>
       </c>
       <c r="I34" s="14" t="n">
         <f aca="false">I32*I33</f>
-        <v>12.6360148309229</v>
+        <v>12.6376377889177</v>
       </c>
       <c r="J34" s="14" t="n">
         <f aca="false">J32*J33</f>
-        <v>12.2740453269244</v>
+        <v>12.2758320047864</v>
       </c>
       <c r="K34" s="14" t="n">
         <f aca="false">K32*K33</f>
-        <v>11.8221408569346</v>
+        <v>11.8240642279237</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">SUM(B34:K34)</f>
-        <v>124.978316826492</v>
+        <v>124.989060057692</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="B39" s="14" t="n">
         <f aca="false">B38*(1-$B$10/$B$16)/($B$18-$B$10)</f>
-        <v>424.683711913359</v>
+        <v>424.822829570188</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>87</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B40" s="14" t="n">
         <f aca="false">B39/(1+$B$18)^9.5</f>
-        <v>192.540893243905</v>
+        <v>192.635300861157</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B41" s="14" t="n">
         <f aca="false">B37+B40</f>
-        <v>317.519210070398</v>
+        <v>317.624360918849</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B42" s="14" t="n">
         <f aca="false">B41+$B$19</f>
-        <v>312.519210070398</v>
+        <v>312.624360918849</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">B42/$B$20</f>
-        <v>675.717210963022</v>
+        <v>675.944564148863</v>
       </c>
     </row>
   </sheetData>
